--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>131167677</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131167665</v>
       </c>
       <c r="B4" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>131167676</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131167679</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131167674</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131167668</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167653</v>
+        <v>131167651</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1733,37 +1733,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613336</v>
+        <v>613285</v>
       </c>
       <c r="R11" t="n">
-        <v>6997445</v>
+        <v>6997537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,19 +1781,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167651</v>
+        <v>131167669</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,31 +1826,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1875,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613285</v>
+        <v>613256</v>
       </c>
       <c r="R12" t="n">
-        <v>6997537</v>
+        <v>6997380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,19 +1891,30 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167669</v>
+        <v>131167653</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,37 +1942,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613256</v>
+        <v>613336</v>
       </c>
       <c r="R13" t="n">
-        <v>6997380</v>
+        <v>6997445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,35 +2019,29 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167670</v>
+        <v>131167650</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,26 +2069,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613271</v>
+        <v>613278</v>
       </c>
       <c r="R14" t="n">
-        <v>6997395</v>
+        <v>6997506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Observerad på tre granar inom 10m radie</t>
+          <t>Färska ringhack  på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2150,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167650</v>
+        <v>131167670</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,31 +2179,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2207,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613278</v>
+        <v>613271</v>
       </c>
       <c r="R15" t="n">
-        <v>6997506</v>
+        <v>6997395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack  på tall</t>
+          <t>Observerad på tre granar inom 10m radie</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,6 +2255,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2274,32 +2274,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167658</v>
+        <v>131167655</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613330</v>
+        <v>613285</v>
       </c>
       <c r="R16" t="n">
-        <v>6997326</v>
+        <v>6997398</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,6 +2353,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,32 +2384,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167655</v>
+        <v>131167658</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,7 +2417,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613285</v>
+        <v>613330</v>
       </c>
       <c r="R17" t="n">
-        <v>6997398</v>
+        <v>6997326</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,11 +2463,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,7 +2492,7 @@
         <v>131167671</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131244268</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>131167677</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131167665</v>
       </c>
       <c r="B4" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131167657</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131167656</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>131167676</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131167679</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131167674</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131167668</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167651</v>
+        <v>131167669</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,31 +1716,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1748,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613285</v>
+        <v>613256</v>
       </c>
       <c r="R11" t="n">
-        <v>6997537</v>
+        <v>6997380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,19 +1781,30 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1815,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167669</v>
+        <v>131167653</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,37 +1832,54 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613256</v>
+        <v>613336</v>
       </c>
       <c r="R12" t="n">
-        <v>6997380</v>
+        <v>6997445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,35 +1909,29 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1931,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167653</v>
+        <v>131167651</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,37 +1976,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613336</v>
+        <v>613285</v>
       </c>
       <c r="R13" t="n">
-        <v>6997445</v>
+        <v>6997537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,19 +2024,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167650</v>
+        <v>131167670</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,31 +2069,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613278</v>
+        <v>613271</v>
       </c>
       <c r="R14" t="n">
-        <v>6997506</v>
+        <v>6997395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack  på tall</t>
+          <t>Observerad på tre granar inom 10m radie</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,6 +2145,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2168,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167670</v>
+        <v>131167650</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,26 +2175,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2206,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613271</v>
+        <v>613278</v>
       </c>
       <c r="R15" t="n">
-        <v>6997395</v>
+        <v>6997506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Observerad på tre granar inom 10m radie</t>
+          <t>Färska ringhack  på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2256,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2274,32 +2274,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167655</v>
+        <v>131167658</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613285</v>
+        <v>613330</v>
       </c>
       <c r="R16" t="n">
-        <v>6997398</v>
+        <v>6997326</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,11 +2353,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,32 +2379,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167658</v>
+        <v>131167655</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,7 +2412,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613330</v>
+        <v>613285</v>
       </c>
       <c r="R17" t="n">
-        <v>6997326</v>
+        <v>6997398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,6 +2458,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,7 +2492,7 @@
         <v>131167671</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131167654</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>131167652</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131167660</v>
       </c>
       <c r="B21" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131244268</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>131167677</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131167665</v>
       </c>
       <c r="B4" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131167657</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131167656</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>131167676</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131167679</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131167674</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131167668</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131167669</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>131167653</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>131167651</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>131167670</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131167650</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,32 +2274,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167658</v>
+        <v>131167655</v>
       </c>
       <c r="B16" t="n">
-        <v>57075</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613330</v>
+        <v>613285</v>
       </c>
       <c r="R16" t="n">
-        <v>6997326</v>
+        <v>6997398</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,6 +2353,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,32 +2384,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167655</v>
+        <v>131167658</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,7 +2417,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613285</v>
+        <v>613330</v>
       </c>
       <c r="R17" t="n">
-        <v>6997398</v>
+        <v>6997326</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,11 +2463,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,7 +2492,7 @@
         <v>131167671</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131167654</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>131167652</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131167660</v>
       </c>
       <c r="B21" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131244268</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167669</v>
+        <v>131167653</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,37 +1716,54 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613256</v>
+        <v>613336</v>
       </c>
       <c r="R11" t="n">
-        <v>6997380</v>
+        <v>6997445</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,35 +1793,29 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1821,7 +1832,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167653</v>
+        <v>131167651</v>
       </c>
       <c r="B12" t="n">
         <v>57887</v>
@@ -1849,37 +1860,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613336</v>
+        <v>613285</v>
       </c>
       <c r="R12" t="n">
-        <v>6997445</v>
+        <v>6997537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,19 +1908,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167651</v>
+        <v>131167669</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,31 +1953,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1991,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613285</v>
+        <v>613256</v>
       </c>
       <c r="R13" t="n">
-        <v>6997537</v>
+        <v>6997380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,19 +2018,30 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2274,32 +2274,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167655</v>
+        <v>131167658</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613285</v>
+        <v>613330</v>
       </c>
       <c r="R16" t="n">
-        <v>6997398</v>
+        <v>6997326</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,11 +2353,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,32 +2379,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167658</v>
+        <v>131167655</v>
       </c>
       <c r="B17" t="n">
-        <v>57076</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,7 +2412,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613330</v>
+        <v>613285</v>
       </c>
       <c r="R17" t="n">
-        <v>6997326</v>
+        <v>6997398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,6 +2458,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167653</v>
+        <v>131167669</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,54 +1716,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613336</v>
+        <v>613256</v>
       </c>
       <c r="R11" t="n">
-        <v>6997445</v>
+        <v>6997380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,29 +1776,35 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1832,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167651</v>
+        <v>131167653</v>
       </c>
       <c r="B12" t="n">
         <v>57887</v>
@@ -1860,25 +1849,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613285</v>
+        <v>613336</v>
       </c>
       <c r="R12" t="n">
-        <v>6997537</v>
+        <v>6997445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,14 +1909,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167669</v>
+        <v>131167651</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,26 +1959,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1980,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613256</v>
+        <v>613285</v>
       </c>
       <c r="R13" t="n">
-        <v>6997380</v>
+        <v>6997537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,30 +2029,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2274,32 +2274,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167658</v>
+        <v>131167655</v>
       </c>
       <c r="B16" t="n">
-        <v>57076</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613330</v>
+        <v>613285</v>
       </c>
       <c r="R16" t="n">
-        <v>6997326</v>
+        <v>6997398</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,6 +2353,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,32 +2384,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167655</v>
+        <v>131167658</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,7 +2417,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613285</v>
+        <v>613330</v>
       </c>
       <c r="R17" t="n">
-        <v>6997398</v>
+        <v>6997326</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,11 +2463,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>131167677</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131167665</v>
       </c>
       <c r="B4" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131167657</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131167656</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>131167676</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131167679</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131167674</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131167668</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167669</v>
+        <v>131167651</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,26 +1716,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1743,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613256</v>
+        <v>613285</v>
       </c>
       <c r="R11" t="n">
-        <v>6997380</v>
+        <v>6997537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,30 +1786,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1824,7 +1818,7 @@
         <v>131167653</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167651</v>
+        <v>131167669</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,31 +1953,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1991,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613285</v>
+        <v>613256</v>
       </c>
       <c r="R13" t="n">
-        <v>6997537</v>
+        <v>6997380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,19 +2018,30 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167670</v>
+        <v>131167650</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,26 +2069,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613271</v>
+        <v>613278</v>
       </c>
       <c r="R14" t="n">
-        <v>6997395</v>
+        <v>6997506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Observerad på tre granar inom 10m radie</t>
+          <t>Färska ringhack  på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2150,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167650</v>
+        <v>131167670</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,31 +2179,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2207,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613278</v>
+        <v>613271</v>
       </c>
       <c r="R15" t="n">
-        <v>6997506</v>
+        <v>6997395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack  på tall</t>
+          <t>Observerad på tre granar inom 10m radie</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,6 +2255,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>131167655</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131167671</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131167654</v>
+        <v>131167652</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,25 +2638,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613254</v>
+        <v>613264</v>
       </c>
       <c r="R19" t="n">
-        <v>6997565</v>
+        <v>6997532</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,14 +2694,24 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131167652</v>
+        <v>131167654</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,33 +2766,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613264</v>
+        <v>613254</v>
       </c>
       <c r="R20" t="n">
-        <v>6997532</v>
+        <v>6997565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,24 +2814,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,7 +2851,7 @@
         <v>131167660</v>
       </c>
       <c r="B21" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131244268</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -1705,7 +1705,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167651</v>
+        <v>131167653</v>
       </c>
       <c r="B11" t="n">
         <v>57888</v>
@@ -1733,25 +1733,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613285</v>
+        <v>613336</v>
       </c>
       <c r="R11" t="n">
-        <v>6997537</v>
+        <v>6997445</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,14 +1793,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1832,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167653</v>
+        <v>131167651</v>
       </c>
       <c r="B12" t="n">
         <v>57888</v>
@@ -1843,37 +1860,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613336</v>
+        <v>613285</v>
       </c>
       <c r="R12" t="n">
-        <v>6997445</v>
+        <v>6997537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,19 +1908,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167650</v>
+        <v>131167670</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,31 +2069,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613278</v>
+        <v>613271</v>
       </c>
       <c r="R14" t="n">
-        <v>6997506</v>
+        <v>6997395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack  på tall</t>
+          <t>Observerad på tre granar inom 10m radie</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,6 +2145,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2168,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167670</v>
+        <v>131167650</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,26 +2175,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2206,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613271</v>
+        <v>613278</v>
       </c>
       <c r="R15" t="n">
-        <v>6997395</v>
+        <v>6997506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Observerad på tre granar inom 10m radie</t>
+          <t>Färska ringhack  på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2256,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2274,32 +2274,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167655</v>
+        <v>131167658</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613285</v>
+        <v>613330</v>
       </c>
       <c r="R16" t="n">
-        <v>6997398</v>
+        <v>6997326</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,11 +2353,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,32 +2379,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167658</v>
+        <v>131167655</v>
       </c>
       <c r="B17" t="n">
-        <v>57076</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,7 +2412,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613330</v>
+        <v>613285</v>
       </c>
       <c r="R17" t="n">
-        <v>6997326</v>
+        <v>6997398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,6 +2458,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,7 +2610,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131167652</v>
+        <v>131167654</v>
       </c>
       <c r="B19" t="n">
         <v>57888</v>
@@ -2638,33 +2638,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613264</v>
+        <v>613254</v>
       </c>
       <c r="R19" t="n">
-        <v>6997532</v>
+        <v>6997565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,24 +2686,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2720,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131167654</v>
+        <v>131167652</v>
       </c>
       <c r="B20" t="n">
         <v>57888</v>
@@ -2766,25 +2748,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613254</v>
+        <v>613264</v>
       </c>
       <c r="R20" t="n">
-        <v>6997565</v>
+        <v>6997532</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,14 +2804,24 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167653</v>
+        <v>131167669</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,54 +1716,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613336</v>
+        <v>613256</v>
       </c>
       <c r="R11" t="n">
-        <v>6997445</v>
+        <v>6997380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,29 +1776,35 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1832,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167651</v>
+        <v>131167653</v>
       </c>
       <c r="B12" t="n">
         <v>57888</v>
@@ -1860,25 +1849,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613285</v>
+        <v>613336</v>
       </c>
       <c r="R12" t="n">
-        <v>6997537</v>
+        <v>6997445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,14 +1909,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167669</v>
+        <v>131167651</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,26 +1959,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1980,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613256</v>
+        <v>613285</v>
       </c>
       <c r="R13" t="n">
-        <v>6997380</v>
+        <v>6997537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,30 +2029,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>131167677</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131167665</v>
       </c>
       <c r="B4" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131167657</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131167656</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>131167676</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131167679</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131167674</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131167668</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131167669</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>131167653</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>131167651</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>131167670</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131167650</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>131167658</v>
       </c>
       <c r="B16" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>131167655</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131167671</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131167654</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>131167652</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131167660</v>
       </c>
       <c r="B21" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131244268</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>131167677</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131167665</v>
       </c>
       <c r="B4" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131167657</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131167656</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>131167676</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131167679</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131167674</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131167668</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131167669</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>131167653</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>131167651</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167670</v>
+        <v>131167650</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,26 +2069,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613271</v>
+        <v>613278</v>
       </c>
       <c r="R14" t="n">
-        <v>6997395</v>
+        <v>6997506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Observerad på tre granar inom 10m radie</t>
+          <t>Färska ringhack  på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2150,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167650</v>
+        <v>131167670</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,31 +2179,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2207,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613278</v>
+        <v>613271</v>
       </c>
       <c r="R15" t="n">
-        <v>6997506</v>
+        <v>6997395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack  på tall</t>
+          <t>Observerad på tre granar inom 10m radie</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,6 +2255,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>131167658</v>
       </c>
       <c r="B16" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>131167655</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131167671</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131167654</v>
+        <v>131167660</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>58051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,42 +2621,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613254</v>
+        <v>613263</v>
       </c>
       <c r="R19" t="n">
-        <v>6997565</v>
+        <v>6997532</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,14 +2694,19 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131167652</v>
+        <v>131167654</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,33 +2761,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613264</v>
+        <v>613254</v>
       </c>
       <c r="R20" t="n">
-        <v>6997532</v>
+        <v>6997565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,24 +2809,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2843,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131167660</v>
+        <v>131167652</v>
       </c>
       <c r="B21" t="n">
-        <v>58050</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,21 +2854,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2899,7 +2894,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613263</v>
+        <v>613264</v>
       </c>
       <c r="R21" t="n">
         <v>6997532</v>
@@ -2934,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2939,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,7 +2974,7 @@
         <v>131244268</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 1170-2026 artfynd.xlsx
+++ b/artfynd/A 1170-2026 artfynd.xlsx
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167650</v>
+        <v>131167670</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,31 +2069,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613278</v>
+        <v>613271</v>
       </c>
       <c r="R14" t="n">
-        <v>6997506</v>
+        <v>6997395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack  på tall</t>
+          <t>Observerad på tre granar inom 10m radie</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,6 +2145,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2168,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167670</v>
+        <v>131167650</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,26 +2175,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2206,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613271</v>
+        <v>613278</v>
       </c>
       <c r="R15" t="n">
-        <v>6997395</v>
+        <v>6997506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Observerad på tre granar inom 10m radie</t>
+          <t>Färska ringhack  på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2256,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131167660</v>
+        <v>131167654</v>
       </c>
       <c r="B19" t="n">
-        <v>58051</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,50 +2621,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613263</v>
+        <v>613254</v>
       </c>
       <c r="R19" t="n">
-        <v>6997532</v>
+        <v>6997565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,19 +2686,14 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:47</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,7 +2720,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131167654</v>
+        <v>131167652</v>
       </c>
       <c r="B20" t="n">
         <v>57892</v>
@@ -2761,25 +2748,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613254</v>
+        <v>613264</v>
       </c>
       <c r="R20" t="n">
-        <v>6997565</v>
+        <v>6997532</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,14 +2804,24 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,10 +2848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131167652</v>
+        <v>131167660</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>58051</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,21 +2859,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2894,7 +2899,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613264</v>
+        <v>613263</v>
       </c>
       <c r="R21" t="n">
         <v>6997532</v>
@@ -2929,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,12 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hackspetten syns i profil på ett smalt träd i centrum av den tagna bilden.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
